--- a/diseases/d031/2005-2009.xlsx
+++ b/diseases/d031/2005-2009.xlsx
@@ -1140,9 +1140,6 @@
       <c r="O4" t="n">
         <v>9</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0.01880813123160408</v>
       </c>
@@ -1663,9 +1660,6 @@
       <c r="O7" t="n">
         <v>10</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>0.0208979235906712</v>
       </c>
@@ -2186,9 +2180,6 @@
       <c r="O10" t="n">
         <v>6</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0.01253875415440272</v>
       </c>
@@ -2709,9 +2700,6 @@
       <c r="O13" t="n">
         <v>7</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
       <c r="R13" t="n">
         <v>0.01462854651346984</v>
       </c>
@@ -3232,9 +3220,6 @@
       <c r="O16" t="n">
         <v>10</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>0.0208979235906712</v>
       </c>
@@ -3755,9 +3740,6 @@
       <c r="O19" t="n">
         <v>7</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
       <c r="R19" t="n">
         <v>0.01462854651346984</v>
       </c>
@@ -4278,9 +4260,6 @@
       <c r="O22" t="n">
         <v>9</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0.01880813123160408</v>
       </c>
@@ -4801,9 +4780,6 @@
       <c r="O25" t="n">
         <v>7</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>0.01462854651346984</v>
       </c>
@@ -5324,9 +5300,6 @@
       <c r="O28" t="n">
         <v>4</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0.008359169436268481</v>
       </c>
@@ -5847,9 +5820,6 @@
       <c r="O31" t="n">
         <v>3</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" t="n">
         <v>0.00626937707720136</v>
       </c>
@@ -6370,9 +6340,6 @@
       <c r="O34" t="n">
         <v>6</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0.01253875415440272</v>
       </c>
@@ -6893,9 +6860,6 @@
       <c r="O37" t="n">
         <v>9</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
       <c r="R37" t="n">
         <v>0.01880813123160408</v>
       </c>
@@ -7416,9 +7380,6 @@
       <c r="O40" t="n">
         <v>3</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0.006249151482400281</v>
       </c>
@@ -7939,9 +7900,6 @@
       <c r="O43" t="n">
         <v>4</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>0.008332201976533707</v>
       </c>
@@ -8462,9 +8420,6 @@
       <c r="O46" t="n">
         <v>10</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0.02083050494133427</v>
       </c>
@@ -8985,9 +8940,6 @@
       <c r="O49" t="n">
         <v>12</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>0.02499660592960112</v>
       </c>
@@ -9508,9 +9460,6 @@
       <c r="O52" t="n">
         <v>9</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0.01874745444720084</v>
       </c>
@@ -10031,9 +9980,6 @@
       <c r="O55" t="n">
         <v>10</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>0.02083050494133427</v>
       </c>
@@ -10554,9 +10500,6 @@
       <c r="O58" t="n">
         <v>11</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0.02291355543546769</v>
       </c>
@@ -11077,9 +11020,6 @@
       <c r="O61" t="n">
         <v>2</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0.004166100988266854</v>
       </c>
@@ -11600,9 +11540,6 @@
       <c r="O64" t="n">
         <v>4</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0.008332201976533707</v>
       </c>
@@ -12123,9 +12060,6 @@
       <c r="O67" t="n">
         <v>6</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0.01249830296480056</v>
       </c>
@@ -12646,9 +12580,6 @@
       <c r="O70" t="n">
         <v>15</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0.0312457574120014</v>
       </c>
@@ -13169,9 +13100,6 @@
       <c r="O73" t="n">
         <v>22</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>0.04582711087093538</v>
       </c>
@@ -13692,9 +13620,6 @@
       <c r="O76" t="n">
         <v>13</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>0.02698320400370139</v>
       </c>
@@ -14215,9 +14140,6 @@
       <c r="O79" t="n">
         <v>21</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0.04358825262136378</v>
       </c>
@@ -14738,9 +14660,6 @@
       <c r="O82" t="n">
         <v>20</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0.04151262154415598</v>
       </c>
@@ -15261,9 +15180,6 @@
       <c r="O85" t="n">
         <v>17</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>0.03528572831253259</v>
       </c>
@@ -15784,9 +15700,6 @@
       <c r="O88" t="n">
         <v>24</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0.04981514585298718</v>
       </c>
@@ -16307,9 +16220,6 @@
       <c r="O91" t="n">
         <v>8</v>
       </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
       <c r="R91" t="n">
         <v>0.01660504861766239</v>
       </c>
@@ -16830,9 +16740,6 @@
       <c r="O94" t="n">
         <v>4</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0.008302524308831197</v>
       </c>
@@ -17353,9 +17260,6 @@
       <c r="O97" t="n">
         <v>6</v>
       </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
       <c r="R97" t="n">
         <v>0.01245378646324679</v>
       </c>
@@ -17876,9 +17780,6 @@
       <c r="O100" t="n">
         <v>3</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0.006226893231623397</v>
       </c>
@@ -18399,9 +18300,6 @@
       <c r="O103" t="n">
         <v>7</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>0.0145294175404546</v>
       </c>
@@ -18922,9 +18820,6 @@
       <c r="O106" t="n">
         <v>8</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0.01660504861766239</v>
       </c>
@@ -19445,9 +19340,6 @@
       <c r="O109" t="n">
         <v>15</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0.03113446615811699</v>
       </c>
@@ -19968,9 +19860,6 @@
       <c r="O112" t="n">
         <v>9</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0.01861177153603757</v>
       </c>
@@ -20491,9 +20380,6 @@
       <c r="O115" t="n">
         <v>11</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0.02274772076626814</v>
       </c>
@@ -21014,9 +20900,6 @@
       <c r="O118" t="n">
         <v>12</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0.02481569538138343</v>
       </c>
@@ -21537,9 +21420,6 @@
       <c r="O121" t="n">
         <v>7</v>
       </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
       <c r="R121" t="n">
         <v>0.014475822305807</v>
       </c>
@@ -22060,9 +21940,6 @@
       <c r="O124" t="n">
         <v>14</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>0.02895164461161399</v>
       </c>
@@ -22583,9 +22460,6 @@
       <c r="O127" t="n">
         <v>24</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="R127" t="n">
         <v>0.04963139076276685</v>
       </c>
@@ -23106,9 +22980,6 @@
       <c r="O130" t="n">
         <v>9</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>0.01861177153603757</v>
       </c>
@@ -23629,9 +23500,6 @@
       <c r="O133" t="n">
         <v>3</v>
       </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
       <c r="R133" t="n">
         <v>0.006203923845345857</v>
       </c>
@@ -24152,9 +24020,6 @@
       <c r="O136" t="n">
         <v>15</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>0.03101961922672929</v>
       </c>
@@ -24675,9 +24540,6 @@
       <c r="O139" t="n">
         <v>20</v>
       </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
       <c r="R139" t="n">
         <v>0.04135949230230571</v>
       </c>
@@ -25198,9 +25060,6 @@
       <c r="O142" t="n">
         <v>13</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="R142" t="n">
         <v>0.02688366999649871</v>
       </c>
@@ -25721,9 +25580,6 @@
       <c r="O145" t="n">
         <v>14</v>
       </c>
-      <c r="Q145" t="n">
-        <v>0</v>
-      </c>
       <c r="R145" t="n">
         <v>0.02895164461161399</v>
       </c>
@@ -26244,9 +26100,6 @@
       <c r="O148" t="n">
         <v>12</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="R148" t="n">
         <v>0.02471847383446036</v>
       </c>
@@ -26767,9 +26620,6 @@
       <c r="O151" t="n">
         <v>15</v>
       </c>
-      <c r="Q151" t="n">
-        <v>0</v>
-      </c>
       <c r="R151" t="n">
         <v>0.03089809229307545</v>
       </c>
@@ -27290,9 +27140,6 @@
       <c r="O154" t="n">
         <v>8</v>
       </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
       <c r="R154" t="n">
         <v>0.01647898255630691</v>
       </c>
@@ -27813,9 +27660,6 @@
       <c r="O157" t="n">
         <v>15</v>
       </c>
-      <c r="Q157" t="n">
-        <v>0</v>
-      </c>
       <c r="R157" t="n">
         <v>0.03089809229307545</v>
       </c>
@@ -28336,9 +28180,6 @@
       <c r="O160" t="n">
         <v>20</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="R160" t="n">
         <v>0.04119745639076727</v>
       </c>
@@ -28859,9 +28700,6 @@
       <c r="O163" t="n">
         <v>19</v>
       </c>
-      <c r="Q163" t="n">
-        <v>0</v>
-      </c>
       <c r="R163" t="n">
         <v>0.0391375835712289</v>
       </c>
@@ -29382,9 +29220,6 @@
       <c r="O166" t="n">
         <v>9</v>
       </c>
-      <c r="Q166" t="n">
-        <v>0</v>
-      </c>
       <c r="R166" t="n">
         <v>0.01853885537584527</v>
       </c>
@@ -29905,9 +29740,6 @@
       <c r="O169" t="n">
         <v>7</v>
       </c>
-      <c r="Q169" t="n">
-        <v>0</v>
-      </c>
       <c r="R169" t="n">
         <v>0.01441910973676854</v>
       </c>
@@ -30428,9 +30260,6 @@
       <c r="O172" t="n">
         <v>8</v>
       </c>
-      <c r="Q172" t="n">
-        <v>0</v>
-      </c>
       <c r="R172" t="n">
         <v>0.01647898255630691</v>
       </c>
@@ -30951,9 +30780,6 @@
       <c r="O175" t="n">
         <v>3</v>
       </c>
-      <c r="Q175" t="n">
-        <v>0</v>
-      </c>
       <c r="R175" t="n">
         <v>0.00617961845861509</v>
       </c>
@@ -31474,9 +31300,6 @@
       <c r="O178" t="n">
         <v>6</v>
       </c>
-      <c r="Q178" t="n">
-        <v>0</v>
-      </c>
       <c r="R178" t="n">
         <v>0.01235923691723018</v>
       </c>
@@ -31996,9 +31819,6 @@
       </c>
       <c r="O181" t="n">
         <v>5</v>
-      </c>
-      <c r="Q181" t="n">
-        <v>0</v>
       </c>
       <c r="R181" t="n">
         <v>0.01029936409769182</v>
